--- a/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
+++ b/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pf\IntelliJ\ws\aqa\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F3D14D-24A9-45A0-816A-65D063D740AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D8B0C-5A6C-4AE5-B067-C6CEC4EF9F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-345" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19230" yWindow="2940" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SNCImport" sheetId="6" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="116">
   <si>
     <t>machine id</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>Table - Gantry Iso Z (mm)</t>
+  </si>
+  <si>
+    <t>Maximum R (mm)</t>
   </si>
 </sst>
 </file>
@@ -827,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -905,6 +908,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2192,7 +2198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C888577F-D905-495E-A65E-9EC6EA2BB2E5}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -2287,6 +2293,15 @@
       <c r="C12" s="22">
         <f>Collimator!L2</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="34">
+        <f>MAX(Data!I3:I11)</f>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
+++ b/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pf\IntelliJ\ws\aqa\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318D8B0C-5A6C-4AE5-B067-C6CEC4EF9F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28557CAA-2AD9-430F-BE87-F4637D067117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19230" yWindow="2940" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-345" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SNCImport" sheetId="6" r:id="rId1"/>
@@ -201,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="117">
   <si>
     <t>machine id</t>
   </si>
@@ -566,6 +566,9 @@
   </si>
   <si>
     <t>Maximum R (mm)</t>
+  </si>
+  <si>
+    <t>Maximum R Table 0 (mm)</t>
   </si>
 </sst>
 </file>
@@ -906,11 +909,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2198,7 +2201,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C888577F-D905-495E-A65E-9EC6EA2BB2E5}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:C13"/>
+  <dimension ref="B2:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -2299,9 +2302,18 @@
       <c r="B13" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="33">
         <f>MAX(Data!I3:I11)</f>
         <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="22">
+        <f>_xlfn.MAXIFS(Preprocess!F3:I11, Preprocess!C3:F11, 0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5447,12 +5459,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
       <c r="L2" s="23">
         <f>MAX(L4:L6)</f>
         <v>0</v>

--- a/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
+++ b/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pf\IntelliJ\ws\aqa\src\main\resources\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umhealth-my.sharepoint.com/personal/irrer_med_umich_edu/Documents/tmp/WLExcel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28557CAA-2AD9-430F-BE87-F4637D067117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{28557CAA-2AD9-430F-BE87-F4637D067117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{774EFE63-7C61-4EA7-AC5E-2BB40B668995}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-345" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SNCImport" sheetId="6" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <definedName name="solver_eng" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
@@ -72,6 +73,7 @@
     <definedName name="solver_neg" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
@@ -79,6 +81,7 @@
     <definedName name="solver_num" localSheetId="4" hidden="1">4</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
@@ -86,6 +89,7 @@
     <definedName name="solver_opt" localSheetId="4" hidden="1">Collimator!$L$2</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">Data!$B$3</definedName>
     <definedName name="solver_opt" localSheetId="5" hidden="1">Report!$K$4</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">SNCImport!$A$1</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
@@ -149,14 +153,17 @@
     <definedName name="solver_typ" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -461,9 +468,6 @@
     <t>CBCT - Gantry Iso Z (mm)</t>
   </si>
   <si>
-    <t>Table - Gantry Iso X (mm)</t>
-  </si>
-  <si>
     <t>Col-Gantry misalignment (mm)</t>
   </si>
   <si>
@@ -562,13 +566,16 @@
     <t>No Table Data</t>
   </si>
   <si>
-    <t>Table - Gantry Iso Z (mm)</t>
-  </si>
-  <si>
     <t>Maximum R (mm)</t>
   </si>
   <si>
     <t>Maximum R Table 0 (mm)</t>
+  </si>
+  <si>
+    <t>Table + Gantry Iso X (mm)</t>
+  </si>
+  <si>
+    <t>Table + Gantry Iso Z (mm)</t>
   </si>
 </sst>
 </file>
@@ -1265,6 +1272,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1272,7 +1280,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2237,19 +2244,19 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="C5" s="22"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C6" s="22"/>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="22" t="str">
         <f>Analysis!O3</f>
@@ -2258,7 +2265,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="22" t="e">
         <f>Analysis!P3</f>
@@ -2267,7 +2274,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="22" t="str">
         <f>Analysis!T1</f>
@@ -2276,13 +2283,13 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="22"/>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="22">
         <f>Analysis!O8</f>
@@ -2291,7 +2298,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C12" s="22">
         <f>Collimator!L2</f>
@@ -2300,7 +2307,7 @@
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C13" s="33">
         <f>MAX(Data!I3:I11)</f>
@@ -2309,7 +2316,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C14" s="22">
         <f>_xlfn.MAXIFS(Preprocess!F3:I11, Preprocess!C3:F11, 0)</f>
@@ -2352,13 +2359,13 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>109</v>
       </c>
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
@@ -2451,7 +2458,7 @@
         <v>21</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X2" s="26" t="s">
         <v>80</v>
@@ -2462,13 +2469,13 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="26">
         <v>-1</v>
@@ -2525,27 +2532,27 @@
         <v>-1</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y3" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="26">
         <v>-1</v>
@@ -2602,27 +2609,27 @@
         <v>-1</v>
       </c>
       <c r="V4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y4" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" s="26">
         <v>-1</v>
@@ -2679,27 +2686,27 @@
         <v>-1</v>
       </c>
       <c r="V5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y5" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="26">
         <v>-1</v>
@@ -2756,27 +2763,27 @@
         <v>-1</v>
       </c>
       <c r="V6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="26">
         <v>-1</v>
@@ -2833,27 +2840,27 @@
         <v>-1</v>
       </c>
       <c r="V7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y7" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" s="26">
         <v>-1</v>
@@ -2910,27 +2917,27 @@
         <v>-1</v>
       </c>
       <c r="V8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y8" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="26">
         <v>-1</v>
@@ -2987,27 +2994,27 @@
         <v>-1</v>
       </c>
       <c r="V9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="26">
         <v>-1</v>
@@ -3064,27 +3071,27 @@
         <v>-1</v>
       </c>
       <c r="V10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y10" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="26">
         <v>-1</v>
@@ -3141,16 +3148,16 @@
         <v>-1</v>
       </c>
       <c r="V11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="X11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y11" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -3345,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
@@ -5014,13 +5021,13 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="N6" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="N6" s="22" t="s">
+      <c r="O6" s="22" t="s">
         <v>95</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>96</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1" t="e">
@@ -5135,7 +5142,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q8" s="1" t="e">
         <f>-(F8-I$8)</f>
@@ -5292,7 +5299,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -5460,7 +5467,7 @@
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H2" s="34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" s="34"/>
       <c r="J2" s="34"/>
@@ -5470,12 +5477,12 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11" t="s">
@@ -5491,13 +5498,13 @@
         <v>32</v>
       </c>
       <c r="J3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -5901,7 +5908,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="3:6" x14ac:dyDescent="0.25">
@@ -5909,7 +5916,7 @@
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="3:6" x14ac:dyDescent="0.25">
@@ -5925,7 +5932,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="3:6" x14ac:dyDescent="0.25">
@@ -5941,7 +5948,7 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
+++ b/src/main/resources/static/WLIsoCheckTemplate__9_Beams.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://umhealth-my.sharepoint.com/personal/irrer_med_umich_edu/Documents/tmp/WLExcel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\tmp\aqaExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{28557CAA-2AD9-430F-BE87-F4637D067117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{774EFE63-7C61-4EA7-AC5E-2BB40B668995}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1ADECE-71F8-4FC4-BCC2-60B4B5CC4441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="117">
   <si>
     <t>machine id</t>
   </si>
@@ -557,9 +557,6 @@
     <t>Winston-Lutz Field Data</t>
   </si>
   <si>
-    <t>To re-calculate spreadsheet in Excel, use CTRL-ALT-F9 and then run the solver on each of the Analysis and Collimator sheets.</t>
-  </si>
-  <si>
     <t>Gantry Flex (mm)</t>
   </si>
   <si>
@@ -576,6 +573,12 @@
   </si>
   <si>
     <t>Table + Gantry Iso Z (mm)</t>
+  </si>
+  <si>
+    <t>To re-calculate spreadsheet in Excel:
+    1: CTRL-ALT-F9 to calculate values
+    2: Set Excel's Solver to use "Evolutionary" (not "GRG Nonlinear")
+    3: Run the solver on each of the Analysis and Collimator sheets</t>
   </si>
 </sst>
 </file>
@@ -840,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -921,6 +924,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2208,14 +2223,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C888577F-D905-495E-A65E-9EC6EA2BB2E5}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:C14"/>
+  <dimension ref="B2:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
         <v>83</v>
       </c>
@@ -2224,7 +2239,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="21" t="s">
         <v>84</v>
       </c>
@@ -2233,7 +2248,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="21" t="s">
         <v>85</v>
       </c>
@@ -2242,28 +2257,60 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="E5" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="35"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="22"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>116</v>
-      </c>
       <c r="C6" s="22"/>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="35"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="22" t="str">
         <f>Analysis!O3</f>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="35"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="21" t="s">
         <v>86</v>
       </c>
@@ -2271,8 +2318,17 @@
         <f>Analysis!P3</f>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
         <v>87</v>
       </c>
@@ -2281,13 +2337,13 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C10" s="22"/>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
         <v>90</v>
       </c>
@@ -2296,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
         <v>91</v>
       </c>
@@ -2305,18 +2361,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="33">
         <f>MAX(Data!I3:I11)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="22">
         <f>_xlfn.MAXIFS(Preprocess!F3:I11, Preprocess!C3:F11, 0)</f>
@@ -2325,6 +2381,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="E5:M8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3302,11 +3361,13 @@
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="G17" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
       <c r="L17" s="32"/>
       <c r="M17" s="32"/>
       <c r="N17" s="32"/>
@@ -3322,10 +3383,22 @@
       <c r="X17" s="32"/>
       <c r="Y17" s="32"/>
     </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+    </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>40</v>
       </c>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -3337,6 +3410,11 @@
       <c r="C20" t="s">
         <v>43</v>
       </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -3351,9 +3429,7 @@
         <f t="shared" ref="C21" si="0">10*(C24-C23)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="28" t="s">
-        <v>110</v>
-      </c>
+      <c r="G21" s="28"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="27">
@@ -3385,6 +3461,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="G17:K20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -5299,7 +5378,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
